--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00792B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00792B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FACC41E3-68EC-4677-8F12-4E524F129D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{481607E6-C4EF-4583-A62E-CD242B328AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DEF84C8F-022A-4CF5-9C93-5EFF02E8A458}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7B623A1B-5A1A-4F17-9431-9F601E512D1C}"/>
   </bookViews>
   <sheets>
     <sheet name="00792B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1547,25 +1547,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBFEA2AA-FD3E-453A-A7E3-45EC570B6CA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1835DB-90F9-4768-87D5-E0E5EDE77C2C}">
   <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1623,7 +1623,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1719,7 +1719,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2019</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39" t="s">
         <v>68</v>
       </c>
